--- a/data/chapter20_ggplot2.xlsx
+++ b/data/chapter20_ggplot2.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kyowapharma-my.sharepoint.com/personal/araya-t_kyowayakuhin_co_jp/Documents/R_scripts/R入門/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{071D272C-90E8-4D1E-A9BA-6ED0E8347A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B748E3D-B7B6-40FB-9B83-8B3C14FCE63F}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109C0D98-DFBD-426C-A395-60717761D246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{6DDDDCA6-070A-4DF6-A17E-AB0DD6972780}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="16440" xr2:uid="{6DDDDCA6-070A-4DF6-A17E-AB0DD6972780}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -485,14 +480,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -530,7 +521,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -636,7 +627,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -778,7 +769,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -787,14 +778,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA7E768-2B34-4640-842B-E88F388CEE8B}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.296875" customWidth="1"/>
-    <col min="2" max="2" width="38.69921875" customWidth="1"/>
-    <col min="3" max="3" width="39.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="38.75" customWidth="1"/>
+    <col min="3" max="3" width="39.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -805,7 +796,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -816,7 +807,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -827,7 +818,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -838,7 +829,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -849,7 +840,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -860,7 +851,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -871,7 +862,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -882,7 +873,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -893,7 +884,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -904,7 +895,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -915,7 +906,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -926,7 +917,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -937,7 +928,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -948,7 +939,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -959,7 +950,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -970,7 +961,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -981,7 +972,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -992,7 +983,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -1003,7 +994,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1014,7 +1005,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1025,7 +1016,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1036,7 +1027,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1047,7 +1038,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -1058,7 +1049,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -1072,5 +1063,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>